--- a/data/trans_dic/P19D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,13</t>
+          <t>1,99; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 20,13</t>
+          <t>11,23; 20,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 17,61</t>
+          <t>8,94; 17,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,78</t>
+          <t>3,75; 10,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,74</t>
+          <t>2,57; 8,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 19,42</t>
+          <t>10,26; 20,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,6</t>
+          <t>9,18; 18,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,73</t>
+          <t>1,76; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,21</t>
+          <t>2,97; 7,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 18,77</t>
+          <t>11,81; 18,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 16,19</t>
+          <t>10,28; 16,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,91</t>
+          <t>3,24; 6,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 14,64</t>
+          <t>8,14; 14,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 22,63</t>
+          <t>14,46; 22,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,99</t>
+          <t>3,34; 8,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,8</t>
+          <t>4,49; 11,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,74</t>
+          <t>7,14; 12,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 15,47</t>
+          <t>9,35; 15,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,69</t>
+          <t>2,93; 7,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,24</t>
+          <t>3,43; 7,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,29</t>
+          <t>8,44; 12,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,96</t>
+          <t>12,86; 17,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,84</t>
+          <t>3,68; 6,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,13</t>
+          <t>4,27; 8,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,88</t>
+          <t>4,02; 10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 20,33</t>
+          <t>11,28; 19,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,78</t>
+          <t>5,42; 11,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,19</t>
+          <t>3,47; 8,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,94</t>
+          <t>3,05; 8,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 19,02</t>
+          <t>10,82; 18,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,03</t>
+          <t>6,0; 11,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,08</t>
+          <t>3,07; 6,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,0</t>
+          <t>4,17; 8,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,83</t>
+          <t>12,2; 18,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,85</t>
+          <t>6,36; 10,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,59</t>
+          <t>3,91; 6,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,74</t>
+          <t>4,13; 10,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 16,35</t>
+          <t>8,61; 16,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,78</t>
+          <t>7,74; 15,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,74</t>
+          <t>1,57; 7,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,95</t>
+          <t>2,77; 7,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,61</t>
+          <t>6,35; 12,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,83</t>
+          <t>5,8; 12,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,34</t>
+          <t>1,54; 4,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,02</t>
+          <t>4,12; 8,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 13,02</t>
+          <t>8,17; 12,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,07</t>
+          <t>7,58; 12,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,44</t>
+          <t>1,93; 5,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 11,76</t>
+          <t>3,63; 11,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,78</t>
+          <t>9,27; 19,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,54</t>
+          <t>3,87; 13,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,35</t>
+          <t>5,31; 11,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,5</t>
+          <t>4,29; 13,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 17,18</t>
+          <t>8,23; 17,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 19,12</t>
+          <t>7,62; 19,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,63</t>
+          <t>4,48; 8,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,73</t>
+          <t>4,76; 10,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 16,83</t>
+          <t>10,15; 16,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,4</t>
+          <t>7,17; 15,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,68</t>
+          <t>5,35; 9,39</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,71</t>
+          <t>3,08; 10,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,31</t>
+          <t>10,85; 20,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,41</t>
+          <t>6,41; 14,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,51</t>
+          <t>3,64; 8,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,87</t>
+          <t>1,98; 7,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,91</t>
+          <t>10,61; 18,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,06</t>
+          <t>4,74; 11,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,5</t>
+          <t>4,19; 9,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,96</t>
+          <t>3,21; 7,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,99</t>
+          <t>11,51; 17,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,72</t>
+          <t>6,35; 11,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,84</t>
+          <t>4,41; 7,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,09</t>
+          <t>5,31; 10,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,79</t>
+          <t>9,1; 14,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,78</t>
+          <t>6,07; 11,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 9,15</t>
+          <t>4,49; 9,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,71</t>
+          <t>4,74; 9,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,38</t>
+          <t>6,77; 11,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,63</t>
+          <t>6,74; 12,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,06</t>
+          <t>3,66; 6,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,4</t>
+          <t>5,46; 8,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,28</t>
+          <t>8,58; 12,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,17</t>
+          <t>6,95; 10,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,45</t>
+          <t>4,57; 7,44</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,35</t>
+          <t>4,06; 8,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,53</t>
+          <t>8,09; 13,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,02</t>
+          <t>7,81; 13,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,2; 74,06</t>
+          <t>14,16; 19,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,07</t>
+          <t>5,57; 10,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,84</t>
+          <t>6,69; 10,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,65</t>
+          <t>7,27; 11,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,21</t>
+          <t>8,39; 12,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,52</t>
+          <t>5,44; 8,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,39</t>
+          <t>7,93; 11,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,29</t>
+          <t>8,25; 11,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,6; 54,39</t>
+          <t>11,74; 15,01</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,27</t>
+          <t>6,27; 8,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,88</t>
+          <t>12,34; 15,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,49</t>
+          <t>8,12; 10,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,87; 36,7</t>
+          <t>7,56; 9,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,72</t>
+          <t>5,82; 7,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,12</t>
+          <t>9,93; 12,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,94</t>
+          <t>7,83; 9,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,22</t>
+          <t>5,19; 6,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,66</t>
+          <t>6,22; 7,69</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,33; 13,07</t>
+          <t>11,38; 13,16</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8,29; 9,73</t>
+          <t>8,31; 9,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 21,5</t>
+          <t>6,51; 7,83</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>27826</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3790; 15577</t>
+          <t>3813; 15240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27236; 50448</t>
+          <t>28130; 51278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21449; 43180</t>
+          <t>21922; 43866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10561; 39034</t>
+          <t>11281; 30663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5000; 17580</t>
+          <t>5167; 17360</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24819; 48777</t>
+          <t>25786; 50286</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22778; 43357</t>
+          <t>22613; 44529</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5479; 13596</t>
+          <t>5452; 14755</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11567; 28301</t>
+          <t>11664; 28964</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59951; 94175</t>
+          <t>59248; 91774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50331; 79599</t>
+          <t>50532; 81075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18894; 52844</t>
+          <t>19786; 40680</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40560</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65255</t>
+          <t>63938</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33572; 60008</t>
+          <t>33351; 59914</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57657; 91961</t>
+          <t>58745; 93234</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12377; 29026</t>
+          <t>12145; 29098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24992; 65325</t>
+          <t>23397; 61911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30270; 56228</t>
+          <t>31521; 54407</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39939; 67730</t>
+          <t>40923; 68329</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11414; 30237</t>
+          <t>11537; 29710</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17482; 36498</t>
+          <t>18303; 38657</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69685; 104576</t>
+          <t>71846; 109485</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106934; 151605</t>
+          <t>108508; 150512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27223; 51715</t>
+          <t>27857; 51394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46738; 92581</t>
+          <t>45105; 84908</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>33139</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9714; 25738</t>
+          <t>9504; 25184</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34803; 59517</t>
+          <t>33030; 57686</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15838; 34222</t>
+          <t>15732; 33018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10544; 24972</t>
+          <t>10539; 24733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8241; 22938</t>
+          <t>8803; 23749</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36016; 62514</t>
+          <t>35558; 61797</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18133; 37022</t>
+          <t>18452; 36608</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10134; 23811</t>
+          <t>10494; 23725</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20814; 42023</t>
+          <t>21920; 42533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77142; 110802</t>
+          <t>75847; 113035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38905; 64935</t>
+          <t>38021; 63586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23814; 42224</t>
+          <t>25230; 44205</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>23872</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11060; 28729</t>
+          <t>11045; 27914</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25559; 50882</t>
+          <t>26784; 50347</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25479; 48769</t>
+          <t>25560; 50171</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5005; 23989</t>
+          <t>5820; 28995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8834; 23798</t>
+          <t>8309; 23260</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21871; 42983</t>
+          <t>21662; 41929</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19361; 41262</t>
+          <t>20251; 42914</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5134; 15815</t>
+          <t>6462; 16945</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23805; 45498</t>
+          <t>23359; 46742</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789; 84940</t>
+          <t>53302; 84656</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50784; 81962</t>
+          <t>51440; 84055</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12329; 34777</t>
+          <t>15277; 40637</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>29068</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5864; 20023</t>
+          <t>6186; 18860</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17450; 36247</t>
+          <t>17889; 37428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4773; 16145</t>
+          <t>4611; 16124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6574; 15741</t>
+          <t>10047; 22478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7678; 23473</t>
+          <t>7461; 22820</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15917; 33417</t>
+          <t>16001; 34856</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12072; 27816</t>
+          <t>11090; 27752</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7411; 15438</t>
+          <t>9854; 19410</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17062; 36935</t>
+          <t>16394; 35572</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39381; 65217</t>
+          <t>39316; 65383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19108; 38110</t>
+          <t>18972; 39696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16352; 28471</t>
+          <t>21891; 38399</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5961; 20262</t>
+          <t>5827; 19974</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27595; 50561</t>
+          <t>27006; 50208</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15539; 33667</t>
+          <t>14973; 33843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9323; 21605</t>
+          <t>9066; 21980</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4728; 16099</t>
+          <t>4054; 16130</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26151; 50085</t>
+          <t>28109; 49913</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11685; 27322</t>
+          <t>11715; 28656</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9628; 20989</t>
+          <t>10564; 22799</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13041; 31326</t>
+          <t>12622; 31410</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59707; 92435</t>
+          <t>59146; 90905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30633; 56332</t>
+          <t>30518; 55996</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22323; 39260</t>
+          <t>22132; 40062</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>45062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>68644</t>
+          <t>83148</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24856; 46945</t>
+          <t>24687; 47080</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53046; 85014</t>
+          <t>52317; 84512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26875; 51975</t>
+          <t>26768; 51169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22713; 54270</t>
+          <t>30946; 64340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24074; 46992</t>
+          <t>25543; 48533</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41997; 71116</t>
+          <t>42309; 71905</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33490; 61332</t>
+          <t>32725; 59896</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15566; 50128</t>
+          <t>27056; 50237</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>53300; 84355</t>
+          <t>54846; 87307</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103341; 147425</t>
+          <t>103014; 148164</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65231; 103543</t>
+          <t>64391; 100820</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>41110; 91555</t>
+          <t>65386; 106347</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>350464</t>
+          <t>127477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>82042</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>423798</t>
+          <t>209520</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22372; 44013</t>
+          <t>21395; 42915</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>50551; 85233</t>
+          <t>50933; 84239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52680; 83265</t>
+          <t>49901; 84007</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>138035; 672425</t>
+          <t>109083; 150350</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32947; 59629</t>
+          <t>32984; 61188</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45496; 75919</t>
+          <t>46883; 75521</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50017; 80517</t>
+          <t>50236; 80884</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>59590; 93135</t>
+          <t>68040; 97927</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60355; 95352</t>
+          <t>60852; 95406</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>104537; 151487</t>
+          <t>105458; 151542</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>107912; 150241</t>
+          <t>109824; 152731</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>203280; 877328</t>
+          <t>185647; 237437</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>151457; 203230</t>
+          <t>154159; 204118</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>355589; 432742</t>
+          <t>358780; 437270</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>216888; 279167</t>
+          <t>216282; 275981</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>264103; 1231091</t>
+          <t>256671; 328757</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>159488; 211701</t>
+          <t>159527; 212697</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>310960; 381103</t>
+          <t>312089; 383088</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>224481; 284889</t>
+          <t>224495; 283527</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>153103; 222707</t>
+          <t>188175; 238187</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327531; 397914</t>
+          <t>323118; 399839</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>685550; 790818</t>
+          <t>688484; 796289</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>458366; 538181</t>
+          <t>459685; 546080</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>441272; 1491175</t>
+          <t>457186; 550184</t>
         </is>
       </c>
     </row>
